--- a/rtss-pre1917/charts/birth-death-counts/adjusted-stage2-final/Забайкальская обл.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/adjusted-stage2-final/Забайкальская обл.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DAE819-EF84-4036-AE7F-4B1108842630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FB5DA8-914A-4BD3-A245-08AA59603048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="УГВИ до и после" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t xml:space="preserve">Числа рождений и смертей для </t>
   </si>
@@ -60,6 +64,27 @@
   </si>
   <si>
     <t>adjusted</t>
+  </si>
+  <si>
+    <t>УГВИ до и после коррекции</t>
+  </si>
+  <si>
+    <t>УГВИ после</t>
+  </si>
+  <si>
+    <t>УГВИ до</t>
+  </si>
+  <si>
+    <t>р-угви-после</t>
+  </si>
+  <si>
+    <t>с-угви-после</t>
+  </si>
+  <si>
+    <t>р-угви-до</t>
+  </si>
+  <si>
+    <t>с-угви-до</t>
   </si>
   <si>
     <t>Забайкальская обл.</t>
@@ -105,7 +130,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,6 +140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -131,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -149,12 +180,25 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -958,6 +1002,1340 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'УГВИ до и после'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>р-угви-после</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$A$6:$A$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$B$6:$B$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1030</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1040</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1060</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1070</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1090</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1210</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1220</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1230</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1240</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1260</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1270</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1290</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1310</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1320</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1330</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0CBE-4EA7-ABAB-36F73D6AF021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'УГВИ до и после'!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>с-угви-после</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$A$6:$A$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$C$6:$C$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1030</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1040</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0CBE-4EA7-ABAB-36F73D6AF021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'УГВИ до и после'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>р-угви-до</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$A$6:$A$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$D$6:$D$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1130</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1160</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1180</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1190</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1210</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1220</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1230</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1240</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1260</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1270</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1290</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1310</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1320</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1330</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1340</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1360</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1370</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1380</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1390</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1410</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1420</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1430</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1440</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0CBE-4EA7-ABAB-36F73D6AF021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'УГВИ до и после'!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>с-угви-до</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$A$6:$A$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'УГВИ до и после'!$E$6:$E$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1030</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1040</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1060</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1070</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1090</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1130</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1140</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0CBE-4EA7-ABAB-36F73D6AF021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1552174576"/>
+        <c:axId val="1359560016"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1552174576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1915"/>
+          <c:min val="1880"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1359560016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1359560016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1552174576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400" b="1" i="0" baseline="0">
+          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -998,7 +2376,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1555,6 +3489,675 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>638174</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>27622</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41EA4D9F-122E-7777-E37C-3EA6BB594914}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="data"/>
+      <sheetName val="УГВИ до и после"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>р-угви-после</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>с-угви-после</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>р-угви-до</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>с-угви-до</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1880</v>
+          </cell>
+          <cell r="B6">
+            <v>1000</v>
+          </cell>
+          <cell r="C6">
+            <v>700</v>
+          </cell>
+          <cell r="D6">
+            <v>1100</v>
+          </cell>
+          <cell r="E6">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1881</v>
+          </cell>
+          <cell r="B7">
+            <v>1010</v>
+          </cell>
+          <cell r="C7">
+            <v>710</v>
+          </cell>
+          <cell r="D7">
+            <v>1110</v>
+          </cell>
+          <cell r="E7">
+            <v>810</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1882</v>
+          </cell>
+          <cell r="B8">
+            <v>1020</v>
+          </cell>
+          <cell r="C8">
+            <v>720</v>
+          </cell>
+          <cell r="D8">
+            <v>1120</v>
+          </cell>
+          <cell r="E8">
+            <v>820</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1883</v>
+          </cell>
+          <cell r="B9">
+            <v>1030</v>
+          </cell>
+          <cell r="C9">
+            <v>730</v>
+          </cell>
+          <cell r="D9">
+            <v>1130</v>
+          </cell>
+          <cell r="E9">
+            <v>830</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1884</v>
+          </cell>
+          <cell r="B10">
+            <v>1040</v>
+          </cell>
+          <cell r="C10">
+            <v>740</v>
+          </cell>
+          <cell r="D10">
+            <v>1140</v>
+          </cell>
+          <cell r="E10">
+            <v>840</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1885</v>
+          </cell>
+          <cell r="B11">
+            <v>1050</v>
+          </cell>
+          <cell r="C11">
+            <v>750</v>
+          </cell>
+          <cell r="D11">
+            <v>1150</v>
+          </cell>
+          <cell r="E11">
+            <v>850</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1886</v>
+          </cell>
+          <cell r="B12">
+            <v>1060</v>
+          </cell>
+          <cell r="C12">
+            <v>760</v>
+          </cell>
+          <cell r="D12">
+            <v>1160</v>
+          </cell>
+          <cell r="E12">
+            <v>860</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1887</v>
+          </cell>
+          <cell r="B13">
+            <v>1070</v>
+          </cell>
+          <cell r="C13">
+            <v>770</v>
+          </cell>
+          <cell r="D13">
+            <v>1170</v>
+          </cell>
+          <cell r="E13">
+            <v>870</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1888</v>
+          </cell>
+          <cell r="B14">
+            <v>1080</v>
+          </cell>
+          <cell r="C14">
+            <v>780</v>
+          </cell>
+          <cell r="D14">
+            <v>1180</v>
+          </cell>
+          <cell r="E14">
+            <v>880</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1889</v>
+          </cell>
+          <cell r="B15">
+            <v>1090</v>
+          </cell>
+          <cell r="C15">
+            <v>790</v>
+          </cell>
+          <cell r="D15">
+            <v>1190</v>
+          </cell>
+          <cell r="E15">
+            <v>890</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1890</v>
+          </cell>
+          <cell r="B16">
+            <v>1100</v>
+          </cell>
+          <cell r="C16">
+            <v>800</v>
+          </cell>
+          <cell r="D16">
+            <v>1200</v>
+          </cell>
+          <cell r="E16">
+            <v>900</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1891</v>
+          </cell>
+          <cell r="B17">
+            <v>1110</v>
+          </cell>
+          <cell r="C17">
+            <v>810</v>
+          </cell>
+          <cell r="D17">
+            <v>1210</v>
+          </cell>
+          <cell r="E17">
+            <v>910</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1892</v>
+          </cell>
+          <cell r="B18">
+            <v>1120</v>
+          </cell>
+          <cell r="C18">
+            <v>820</v>
+          </cell>
+          <cell r="D18">
+            <v>1220</v>
+          </cell>
+          <cell r="E18">
+            <v>920</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1893</v>
+          </cell>
+          <cell r="B19">
+            <v>1130</v>
+          </cell>
+          <cell r="C19">
+            <v>830</v>
+          </cell>
+          <cell r="D19">
+            <v>1230</v>
+          </cell>
+          <cell r="E19">
+            <v>930</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1894</v>
+          </cell>
+          <cell r="B20">
+            <v>1140</v>
+          </cell>
+          <cell r="C20">
+            <v>840</v>
+          </cell>
+          <cell r="D20">
+            <v>1240</v>
+          </cell>
+          <cell r="E20">
+            <v>940</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>1895</v>
+          </cell>
+          <cell r="B21">
+            <v>1150</v>
+          </cell>
+          <cell r="C21">
+            <v>850</v>
+          </cell>
+          <cell r="D21">
+            <v>1250</v>
+          </cell>
+          <cell r="E21">
+            <v>950</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>1896</v>
+          </cell>
+          <cell r="B22">
+            <v>1160</v>
+          </cell>
+          <cell r="C22">
+            <v>860</v>
+          </cell>
+          <cell r="D22">
+            <v>1260</v>
+          </cell>
+          <cell r="E22">
+            <v>960</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>1897</v>
+          </cell>
+          <cell r="B23">
+            <v>1170</v>
+          </cell>
+          <cell r="C23">
+            <v>870</v>
+          </cell>
+          <cell r="D23">
+            <v>1270</v>
+          </cell>
+          <cell r="E23">
+            <v>970</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>1898</v>
+          </cell>
+          <cell r="B24">
+            <v>1180</v>
+          </cell>
+          <cell r="C24">
+            <v>880</v>
+          </cell>
+          <cell r="D24">
+            <v>1280</v>
+          </cell>
+          <cell r="E24">
+            <v>980</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>1899</v>
+          </cell>
+          <cell r="B25">
+            <v>1190</v>
+          </cell>
+          <cell r="C25">
+            <v>890</v>
+          </cell>
+          <cell r="D25">
+            <v>1290</v>
+          </cell>
+          <cell r="E25">
+            <v>990</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>1900</v>
+          </cell>
+          <cell r="B26">
+            <v>1200</v>
+          </cell>
+          <cell r="C26">
+            <v>900</v>
+          </cell>
+          <cell r="D26">
+            <v>1300</v>
+          </cell>
+          <cell r="E26">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>1901</v>
+          </cell>
+          <cell r="B27">
+            <v>1210</v>
+          </cell>
+          <cell r="C27">
+            <v>910</v>
+          </cell>
+          <cell r="D27">
+            <v>1310</v>
+          </cell>
+          <cell r="E27">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>1902</v>
+          </cell>
+          <cell r="B28">
+            <v>1220</v>
+          </cell>
+          <cell r="C28">
+            <v>920</v>
+          </cell>
+          <cell r="D28">
+            <v>1320</v>
+          </cell>
+          <cell r="E28">
+            <v>1020</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>1903</v>
+          </cell>
+          <cell r="B29">
+            <v>1230</v>
+          </cell>
+          <cell r="C29">
+            <v>930</v>
+          </cell>
+          <cell r="D29">
+            <v>1330</v>
+          </cell>
+          <cell r="E29">
+            <v>1030</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>1904</v>
+          </cell>
+          <cell r="B30">
+            <v>1240</v>
+          </cell>
+          <cell r="C30">
+            <v>940</v>
+          </cell>
+          <cell r="D30">
+            <v>1340</v>
+          </cell>
+          <cell r="E30">
+            <v>1040</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>1905</v>
+          </cell>
+          <cell r="B31">
+            <v>1250</v>
+          </cell>
+          <cell r="C31">
+            <v>950</v>
+          </cell>
+          <cell r="D31">
+            <v>1350</v>
+          </cell>
+          <cell r="E31">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>1906</v>
+          </cell>
+          <cell r="B32">
+            <v>1260</v>
+          </cell>
+          <cell r="C32">
+            <v>960</v>
+          </cell>
+          <cell r="D32">
+            <v>1360</v>
+          </cell>
+          <cell r="E32">
+            <v>1060</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1907</v>
+          </cell>
+          <cell r="B33">
+            <v>1270</v>
+          </cell>
+          <cell r="C33">
+            <v>970</v>
+          </cell>
+          <cell r="D33">
+            <v>1370</v>
+          </cell>
+          <cell r="E33">
+            <v>1070</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1908</v>
+          </cell>
+          <cell r="B34">
+            <v>1280</v>
+          </cell>
+          <cell r="C34">
+            <v>980</v>
+          </cell>
+          <cell r="D34">
+            <v>1380</v>
+          </cell>
+          <cell r="E34">
+            <v>1080</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1909</v>
+          </cell>
+          <cell r="B35">
+            <v>1290</v>
+          </cell>
+          <cell r="C35">
+            <v>990</v>
+          </cell>
+          <cell r="D35">
+            <v>1390</v>
+          </cell>
+          <cell r="E35">
+            <v>1090</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1910</v>
+          </cell>
+          <cell r="B36">
+            <v>1300</v>
+          </cell>
+          <cell r="C36">
+            <v>1000</v>
+          </cell>
+          <cell r="D36">
+            <v>1400</v>
+          </cell>
+          <cell r="E36">
+            <v>1100</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1911</v>
+          </cell>
+          <cell r="B37">
+            <v>1310</v>
+          </cell>
+          <cell r="C37">
+            <v>1010</v>
+          </cell>
+          <cell r="D37">
+            <v>1410</v>
+          </cell>
+          <cell r="E37">
+            <v>1110</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1912</v>
+          </cell>
+          <cell r="B38">
+            <v>1320</v>
+          </cell>
+          <cell r="C38">
+            <v>1020</v>
+          </cell>
+          <cell r="D38">
+            <v>1420</v>
+          </cell>
+          <cell r="E38">
+            <v>1120</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1913</v>
+          </cell>
+          <cell r="B39">
+            <v>1330</v>
+          </cell>
+          <cell r="C39">
+            <v>1030</v>
+          </cell>
+          <cell r="D39">
+            <v>1430</v>
+          </cell>
+          <cell r="E39">
+            <v>1130</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1914</v>
+          </cell>
+          <cell r="B40">
+            <v>1340</v>
+          </cell>
+          <cell r="C40">
+            <v>1040</v>
+          </cell>
+          <cell r="D40">
+            <v>1440</v>
+          </cell>
+          <cell r="E40">
+            <v>1140</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1887,11 +4490,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="10"/>
+      <c r="C1" s="9"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -1900,10 +4503,10 @@
       <c r="K1" s="2"/>
     </row>
     <row r="3" spans="1:30" ht="15.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -1912,13 +4515,13 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:30" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5"/>
@@ -2603,6 +5206,1062 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB399F8A-B7EA-4935-8BC0-ABA200C79F82}">
+  <dimension ref="A1:AH41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.05078125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.9453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.68359375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.7890625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.5234375"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" ht="20.399999999999999" x14ac:dyDescent="0.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+    </row>
+    <row r="6" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6">
+        <v>1880</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+    </row>
+    <row r="7" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6" t="n">
+        <f>A6+1</f>
+        <v>1881.0</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>21913.0</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>13490.0</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>18429.0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>12049.0</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+    </row>
+    <row r="8" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="n">
+        <f t="shared" ref="A8:A40" si="0">A7+1</f>
+        <v>1882.0</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>22265.0</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>13707.0</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>19079.0</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>11825.0</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+    </row>
+    <row r="9" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1883.0</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>22623.0</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>13927.0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>19779.0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>11622.0</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+    </row>
+    <row r="10" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1884.0</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>22987.0</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>14151.0</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>21403.0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>13860.0</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+    </row>
+    <row r="11" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1885.0</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>23356.0</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>14379.0</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>23127.0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>16503.0</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1886.0</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>23732.0</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>14610.0</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>22540.0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>15776.0</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+    </row>
+    <row r="13" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1887.0</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>24114.0</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>14845.0</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>21969.0</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>15082.0</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3"/>
+    </row>
+    <row r="14" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1888.0</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>24502.0</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>15083.0</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>19014.0</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>13823.0</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+    </row>
+    <row r="15" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1889.0</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>24896.0</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>15326.0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>16413.0</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>12635.0</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+    </row>
+    <row r="16" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1890.0</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>25296.0</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>15572.0</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>17375.0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>14436.0</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1891.0</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>25703.0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>15823.0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>20970.0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>12141.0</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+      <c r="AH17" s="3"/>
+    </row>
+    <row r="18" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1892.0</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>26116.0</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>16077.0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>22788.0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>13074.0</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+    </row>
+    <row r="19" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1893.0</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>26536.0</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>16336.0</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>20415.0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>13483.0</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1894.0</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>26963.0</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>16599.0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>24998.0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>16022.0</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+    </row>
+    <row r="21" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1895.0</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>27396.0</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>16866.0</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>24548.0</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>15681.0</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+    </row>
+    <row r="22" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1896.0</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>27837.0</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>17137.0</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>24548.0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>15681.0</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+    </row>
+    <row r="23" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1897.0</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>28285.0</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>17412.0</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>25798.0</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>16694.0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+    </row>
+    <row r="24" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1898.0</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>28740.0</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>17692.0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>24834.0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>16281.0</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+    </row>
+    <row r="25" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1899.0</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>29202.0</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>17977.0</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>25463.0</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>17543.0</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+    </row>
+    <row r="26" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1900.0</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>29671.0</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>18266.0</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>27232.0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>16689.0</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+    </row>
+    <row r="27" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1901.0</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>30149.0</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>18560.0</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>26589.0</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>16144.0</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+    </row>
+    <row r="28" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1902.0</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>30633.0</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>18858.0</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>24960.0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>14802.0</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+    </row>
+    <row r="29" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1903.0</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>31126.0</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>19162.0</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>25288.0</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>16776.0</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+    </row>
+    <row r="30" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1904.0</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>31627.0</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>19470.0</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>26906.0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>19305.0</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+    </row>
+    <row r="31" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1905.0</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>32135.0</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>19783.0</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>24558.0</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>21041.0</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+    </row>
+    <row r="32" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1906.0</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>32652.0</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>20101.0</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>23556.0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>16563.0</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+    </row>
+    <row r="33" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1907.0</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>33177.0</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>20424.0</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>25302.0</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>15046.0</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+    </row>
+    <row r="34" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1908.0</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>34137.0</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>21216.0</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>34137.0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>21216.0</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+    </row>
+    <row r="35" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1909.0</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>35128.0</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>22093.0</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>35128.0</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>22093.0</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="3"/>
+    </row>
+    <row r="36" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1910.0</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>34475.0</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>22354.0</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>34475.0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>22354.0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="3"/>
+    </row>
+    <row r="37" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1911.0</v>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>36828.0</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>20897.0</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>36828.0</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>20897.0</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+    </row>
+    <row r="38" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1912.0</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>34993.0</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>21678.0</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>34993.0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>21678.0</v>
+      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+    </row>
+    <row r="39" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1913.0</v>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>35522.0</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>21658.0</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>35522.0</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>21658.0</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="1:34" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>1914.0</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>37564.0</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>23125.0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>42077.0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>24836.0</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{44ba9367-eb51-4860-91fd-089945178738}" enabled="1" method="Privileged" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
